--- a/data/trans_bre/P16A07-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A07-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 5,92</t>
+          <t>0,98; 5,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 3,27</t>
+          <t>-2,06; 3,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,75</t>
+          <t>0,73; 5,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 3,93</t>
+          <t>-0,59; 3,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,81; 2055,34</t>
+          <t>44,9; 2025,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-68,32; 280,88</t>
+          <t>-67,62; 299,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 1254,52</t>
+          <t>2,51; 995,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 224,77</t>
+          <t>-18,83; 216,22</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 8,03</t>
+          <t>2,27; 8,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 4,45</t>
+          <t>-1,77; 4,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 3,89</t>
+          <t>-0,49; 3,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,49</t>
+          <t>0,92; 5,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,68; 986,92</t>
+          <t>70,64; 1192,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,69; 242,78</t>
+          <t>-46,29; 231,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,89; 737,5</t>
+          <t>-41,28; 615,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,85; 292,84</t>
+          <t>12,79; 296,18</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 9,64</t>
+          <t>1,23; 10,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 10,0</t>
+          <t>1,96; 10,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 14,21</t>
+          <t>3,22; 13,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 11,29</t>
+          <t>2,62; 11,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,22; 534,67</t>
+          <t>22,22; 567,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,42; 297,61</t>
+          <t>34,02; 334,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83,39; 684,42</t>
+          <t>78,54; 678,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>42,87; 915,79</t>
+          <t>50,18; 890,46</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,15</t>
+          <t>2,35; 6,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 6,26</t>
+          <t>1,57; 6,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,73</t>
+          <t>0,88; 4,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 5,14</t>
+          <t>-0,9; 5,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,0; 405,01</t>
+          <t>86,18; 400,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,39; 215,54</t>
+          <t>32,4; 211,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,25; 262,48</t>
+          <t>24,36; 246,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,99; 158,66</t>
+          <t>-13,86; 161,21</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 7,63</t>
+          <t>1,82; 7,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,13; 12,74</t>
+          <t>7,01; 12,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 11,47</t>
+          <t>5,84; 11,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 7,45</t>
+          <t>1,99; 7,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,84; 360,53</t>
+          <t>25,36; 384,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>178,12; 803,4</t>
+          <t>192,18; 844,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>147,01; 595,61</t>
+          <t>143,76; 596,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30,29; 268,41</t>
+          <t>37,6; 270,19</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,62</t>
+          <t>0,15; 5,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,44; 10,26</t>
+          <t>6,45; 10,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,36; 8,48</t>
+          <t>4,34; 8,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,43; 7,98</t>
+          <t>2,68; 7,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,6; 339,7</t>
+          <t>-1,12; 301,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>109,38; 2355,9</t>
+          <t>130,7; 2242,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>58,41; 866,79</t>
+          <t>36,64; 890,15</t>
         </is>
       </c>
     </row>
@@ -1265,37 +1265,37 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,12; 6,38</t>
+          <t>4,04; 6,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,85; 5,97</t>
+          <t>3,97; 6,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,17</t>
+          <t>2,48; 5,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>128,26; 302,06</t>
+          <t>130,25; 297,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>112,42; 242,48</t>
+          <t>112,64; 242,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>147,78; 326,41</t>
+          <t>152,12; 323,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>69,45; 198,26</t>
+          <t>68,17; 191,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A07-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A07-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,61</t>
+          <t>1,75</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>67,04%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,42</t>
+          <t>1,0; 5,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 3,28</t>
+          <t>-2,02; 3,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 5,7</t>
+          <t>0,65; 5,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,86</t>
+          <t>-0,3; 3,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,9; 2025,61</t>
+          <t>30,25; 2001,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-67,62; 299,81</t>
+          <t>-67,26; 255,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 995,62</t>
+          <t>5,75; 1068,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 216,22</t>
+          <t>-13,26; 213,57</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>106,21%</t>
+          <t>107,22%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 8,06</t>
+          <t>1,99; 7,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 4,01</t>
+          <t>-2,07; 3,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,88</t>
+          <t>-0,41; 3,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,56</t>
+          <t>0,61; 5,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>70,64; 1192,6</t>
+          <t>57,9; 931,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,29; 231,48</t>
+          <t>-45,75; 249,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,28; 615,85</t>
+          <t>-37,8; 739,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,79; 296,18</t>
+          <t>6,41; 295,83</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,18</t>
+          <t>4,1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>197,18%</t>
+          <t>89,18%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 10,17</t>
+          <t>1,22; 10,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 10,18</t>
+          <t>2,11; 10,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 13,95</t>
+          <t>3,23; 13,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 11,15</t>
+          <t>0,33; 7,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,22; 567,54</t>
+          <t>26,64; 567,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,02; 334,06</t>
+          <t>35,91; 333,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78,54; 678,28</t>
+          <t>79,82; 658,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50,18; 890,46</t>
+          <t>2,45; 243,74</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,71</t>
+          <t>4,25</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>113,23%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 6,29</t>
+          <t>2,39; 6,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,15</t>
+          <t>1,74; 6,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,6</t>
+          <t>1,14; 4,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 5,09</t>
+          <t>2,45; 6,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,18; 400,42</t>
+          <t>84,34; 394,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,4; 211,61</t>
+          <t>37,22; 212,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,36; 246,69</t>
+          <t>34,91; 256,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 161,21</t>
+          <t>52,68; 208,68</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>6,41</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>121,35%</t>
+          <t>171,94%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 7,75</t>
+          <t>1,33; 7,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,01; 12,47</t>
+          <t>7,18; 12,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,84; 11,4</t>
+          <t>6,13; 11,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 7,84</t>
+          <t>4,12; 8,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,36; 384,17</t>
+          <t>16,05; 354,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>192,18; 844,68</t>
+          <t>184,43; 837,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>143,76; 596,21</t>
+          <t>152,75; 577,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,6; 270,19</t>
+          <t>77,77; 361,9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,89</t>
+          <t>4,92</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>303,45%</t>
+          <t>182,25%</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,15; 5,36</t>
+          <t>0,45; 5,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,45; 10,12</t>
+          <t>6,37; 10,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,34; 8,44</t>
+          <t>4,25; 8,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,87</t>
+          <t>1,53; 7,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 301,05</t>
+          <t>7,97; 360,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>130,7; 2242,25</t>
+          <t>125,55; 2579,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36,64; 890,15</t>
+          <t>15,04; 680,58</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,91</t>
+          <t>4,22</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>120,26%</t>
+          <t>121,22%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,31; 5,35</t>
+          <t>3,32; 5,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,04; 6,35</t>
+          <t>4,1; 6,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,97; 6,04</t>
+          <t>3,9; 5,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,07</t>
+          <t>3,2; 5,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>130,25; 297,43</t>
+          <t>128,16; 288,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>112,64; 242,15</t>
+          <t>116,33; 245,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>152,12; 323,9</t>
+          <t>151,37; 335,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>68,17; 191,48</t>
+          <t>79,91; 169,25</t>
         </is>
       </c>
     </row>
